--- a/public/export/group_list_cn/group_list_cn_tmp.xlsx
+++ b/public/export/group_list_cn/group_list_cn_tmp.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="cqxquPAuvWcxdXwm359tepmiSox2z3kThh4ZyUuwSCE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eWesqA/MpUc51VbW8wBQtqGun16zcFhJB6ls0NNNjnk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>CÔNG TY TNHH VẠN SỰ THÔNG</t>
   </si>
@@ -36,10 +36,7 @@
     <t>生日</t>
   </si>
   <si>
-    <t>电话号码</t>
-  </si>
-  <si>
-    <t>通行证号</t>
+    <t>官方调度号</t>
   </si>
 </sst>
 </file>
@@ -107,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -137,6 +134,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="1" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -356,7 +356,7 @@
     <col customWidth="1" min="2" max="2" width="11.0"/>
     <col customWidth="1" min="3" max="3" width="34.0"/>
     <col customWidth="1" min="4" max="4" width="9.71"/>
-    <col customWidth="1" min="5" max="7" width="18.57"/>
+    <col customWidth="1" min="5" max="6" width="18.57"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
@@ -366,7 +366,6 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1"/>
@@ -390,7 +389,6 @@
       <c r="D5" s="2"/>
       <c r="E5" s="4"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
     </row>
     <row r="6" ht="20.25" customHeight="1">
       <c r="A6" s="5"/>
@@ -406,844 +404,737 @@
       <c r="E6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="7" ht="20.25" customHeight="1">
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" ht="20.25" customHeight="1">
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" ht="20.25" customHeight="1">
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" ht="20.25" customHeight="1">
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" ht="20.25" customHeight="1">
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" ht="20.25" customHeight="1">
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" ht="20.25" customHeight="1">
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" ht="20.25" customHeight="1">
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15" ht="20.25" customHeight="1">
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" ht="20.25" customHeight="1">
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17" ht="20.25" customHeight="1">
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19" ht="20.25" customHeight="1">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20" ht="20.25" customHeight="1">
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21" ht="20.25" customHeight="1">
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" ht="20.25" customHeight="1">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" ht="20.25" customHeight="1">
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" ht="20.25" customHeight="1">
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" ht="20.25" customHeight="1">
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" ht="20.25" customHeight="1">
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" ht="20.25" customHeight="1">
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
     </row>
     <row r="28" ht="20.25" customHeight="1">
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" ht="20.25" customHeight="1">
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" ht="20.25" customHeight="1">
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" ht="20.25" customHeight="1">
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" ht="20.25" customHeight="1">
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" ht="20.25" customHeight="1">
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
     </row>
     <row r="35" ht="20.25" customHeight="1">
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
     </row>
     <row r="36" ht="20.25" customHeight="1">
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
     </row>
     <row r="37" ht="20.25" customHeight="1">
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
     </row>
     <row r="38" ht="20.25" customHeight="1">
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
     </row>
     <row r="39" ht="20.25" customHeight="1">
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
     </row>
     <row r="40" ht="20.25" customHeight="1">
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
     </row>
     <row r="41" ht="20.25" customHeight="1">
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
     </row>
     <row r="42" ht="20.25" customHeight="1">
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
     </row>
     <row r="43" ht="20.25" customHeight="1">
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
     </row>
     <row r="44" ht="20.25" customHeight="1">
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
     </row>
     <row r="45" ht="20.25" customHeight="1">
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
     </row>
     <row r="46" ht="20.25" customHeight="1">
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
     </row>
     <row r="47" ht="20.25" customHeight="1">
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
     </row>
     <row r="48" ht="20.25" customHeight="1">
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" ht="20.25" customHeight="1">
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
     </row>
     <row r="50" ht="20.25" customHeight="1">
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
     </row>
     <row r="51" ht="20.25" customHeight="1">
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
     </row>
     <row r="52" ht="20.25" customHeight="1">
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
     </row>
     <row r="53" ht="20.25" customHeight="1">
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
     </row>
     <row r="54" ht="20.25" customHeight="1">
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
     </row>
     <row r="55" ht="20.25" customHeight="1">
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
     </row>
     <row r="56" ht="20.25" customHeight="1">
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
     </row>
     <row r="57" ht="20.25" customHeight="1">
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
     </row>
     <row r="58" ht="20.25" customHeight="1">
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
     </row>
     <row r="59" ht="20.25" customHeight="1">
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
     </row>
     <row r="60" ht="20.25" customHeight="1">
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
     </row>
     <row r="61" ht="20.25" customHeight="1">
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
     </row>
     <row r="62" ht="20.25" customHeight="1">
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
     </row>
     <row r="63" ht="20.25" customHeight="1">
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
     </row>
     <row r="64" ht="20.25" customHeight="1">
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
     </row>
     <row r="65" ht="20.25" customHeight="1">
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
     </row>
     <row r="66" ht="20.25" customHeight="1">
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
     </row>
     <row r="67" ht="20.25" customHeight="1">
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
     </row>
     <row r="68" ht="20.25" customHeight="1">
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
     </row>
     <row r="69" ht="20.25" customHeight="1">
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
     </row>
     <row r="70" ht="20.25" customHeight="1">
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
     </row>
     <row r="71" ht="20.25" customHeight="1">
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
     </row>
     <row r="72" ht="20.25" customHeight="1">
-      <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
     </row>
     <row r="73" ht="20.25" customHeight="1">
-      <c r="B73" s="10"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
     </row>
     <row r="74" ht="20.25" customHeight="1">
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
     </row>
     <row r="75" ht="20.25" customHeight="1">
-      <c r="B75" s="10"/>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
     </row>
     <row r="76" ht="20.25" customHeight="1">
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
     </row>
     <row r="77" ht="20.25" customHeight="1">
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
     </row>
     <row r="78" ht="20.25" customHeight="1">
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
     </row>
     <row r="79" ht="20.25" customHeight="1">
-      <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
     </row>
     <row r="80" ht="20.25" customHeight="1">
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
     </row>
     <row r="81" ht="20.25" customHeight="1">
-      <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
     </row>
     <row r="82" ht="20.25" customHeight="1">
-      <c r="B82" s="10"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
     </row>
     <row r="83" ht="20.25" customHeight="1">
-      <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
     </row>
     <row r="84" ht="20.25" customHeight="1">
-      <c r="B84" s="10"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="10"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
     </row>
     <row r="85" ht="20.25" customHeight="1">
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
     </row>
     <row r="86" ht="20.25" customHeight="1">
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="10"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
     </row>
     <row r="87" ht="20.25" customHeight="1">
-      <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
     </row>
     <row r="88" ht="20.25" customHeight="1">
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="10"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
     </row>
     <row r="89" ht="20.25" customHeight="1">
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
     </row>
     <row r="90" ht="20.25" customHeight="1">
-      <c r="B90" s="10"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="10"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
     </row>
     <row r="91" ht="20.25" customHeight="1">
-      <c r="B91" s="10"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
     </row>
     <row r="92" ht="20.25" customHeight="1">
-      <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
     </row>
     <row r="93" ht="20.25" customHeight="1">
-      <c r="B93" s="10"/>
-      <c r="C93" s="10"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
     </row>
     <row r="94" ht="20.25" customHeight="1">
-      <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
     </row>
     <row r="95" ht="20.25" customHeight="1">
-      <c r="B95" s="10"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="10"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
     </row>
     <row r="96" ht="20.25" customHeight="1">
-      <c r="B96" s="10"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="10"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
     </row>
     <row r="97" ht="20.25" customHeight="1">
-      <c r="B97" s="10"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="10"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
     </row>
     <row r="98" ht="20.25" customHeight="1">
-      <c r="B98" s="10"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="10"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="10"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
     </row>
     <row r="99" ht="20.25" customHeight="1">
-      <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
-      <c r="E99" s="10"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="10"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
     </row>
     <row r="100" ht="20.25" customHeight="1">
-      <c r="B100" s="10"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="10"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
     </row>
     <row r="101" ht="20.25" customHeight="1">
-      <c r="B101" s="10"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="10"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="10"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
     </row>
     <row r="102" ht="20.25" customHeight="1">
-      <c r="B102" s="10"/>
-      <c r="C102" s="10"/>
-      <c r="D102" s="10"/>
-      <c r="E102" s="10"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="10"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
     </row>
     <row r="103" ht="20.25" customHeight="1">
-      <c r="B103" s="10"/>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
-      <c r="E103" s="10"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="10"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
     </row>
     <row r="104" ht="20.25" customHeight="1">
-      <c r="B104" s="10"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="10"/>
-      <c r="E104" s="10"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="10"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="11"/>
     </row>
     <row r="105" ht="20.25" customHeight="1">
-      <c r="B105" s="10"/>
-      <c r="C105" s="10"/>
-      <c r="D105" s="10"/>
-      <c r="E105" s="10"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="10"/>
+      <c r="B105" s="11"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="11"/>
     </row>
     <row r="106" ht="20.25" customHeight="1">
-      <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
-      <c r="D106" s="10"/>
-      <c r="E106" s="10"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="10"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
     </row>
     <row r="107" ht="20.25" customHeight="1">
-      <c r="B107" s="10"/>
-      <c r="C107" s="10"/>
-      <c r="D107" s="10"/>
-      <c r="E107" s="10"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="10"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
     </row>
     <row r="108" ht="20.25" customHeight="1">
-      <c r="B108" s="10"/>
-      <c r="C108" s="10"/>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="10"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
     </row>
     <row r="109" ht="20.25" customHeight="1">
-      <c r="B109" s="10"/>
-      <c r="C109" s="10"/>
-      <c r="D109" s="10"/>
-      <c r="E109" s="10"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="10"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
     </row>
     <row r="110" ht="20.25" customHeight="1">
-      <c r="B110" s="10"/>
-      <c r="C110" s="10"/>
-      <c r="D110" s="10"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="10"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="11"/>
     </row>
     <row r="111" ht="20.25" customHeight="1"/>
     <row r="112" ht="20.25" customHeight="1"/>
@@ -2131,8 +2022,8 @@
     <row r="994" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G4"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F4"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
